--- a/food_beverage_order_forms/039_luxury_hotel_food_supply_order_request--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/039_luxury_hotel_food_supply_order_request--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'options':_[{'id':_2,_'name':_'deliverydate',_'label':_'delivery_date'},_{'id':_3,_'name':_'deliverytime',_'label':_'delivery_time'}]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'options': [{'id': 2, 'name': 'deliverydate', 'label': 'delivery_date'}, {'id': 3, 'name': 'deliverytime', 'label': 'delivery_time'}]}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'deliveryaddress',_'label':_'delivery_address',_'options':_[]}</t>
+          <t>delivery_address</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'deliveryaddress', 'label': 'delivery_address', 'options': []}</t>
+          <t>delivery address</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_1',_'label':_'select_1'}</t>
+          <t>select_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_1', 'label': 'select_1'}</t>
+          <t>select 1</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_2',_'label':_'select_2'}</t>
+          <t>select_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_2', 'label': 'select_2'}</t>
+          <t>select 2</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'select_3',_'label':_'select_3'}</t>
+          <t>select_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'select_3', 'label': 'select_3'}</t>
+          <t>select 3</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approval_ace_1',_'label':_'approval_ace_1'}</t>
+          <t>approval_ace_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'approval_ace_1', 'label': 'approval_ace_1'}</t>
+          <t>approval ace 1</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approval_ace_2',_'label':_'approval_ace_2'}</t>
+          <t>approval_ace_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'approval_ace_2', 'label': 'approval_ace_2'}</t>
+          <t>approval ace 2</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'approval_ace_3',_'label':_'approval_ace_3'}</t>
+          <t>approval_ace_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'approval_ace_3', 'label': 'approval_ace_3'}</t>
+          <t>approval ace 3</t>
         </is>
       </c>
     </row>
